--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_07-05-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_07-05-2025.xlsx
@@ -1411,17 +1411,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£30.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£30.83</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£30.83</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>**£55.40**-Sale Price old Price: £82.22</t>
+          <t>Error: list index out of range</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£44.42</t>
+          <t>Error: list index out of range</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£48.24</t>
+          <t>£48.12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£48.24</t>
+          <t>£48.12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£48.24</t>
+          <t>£48.12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
